--- a/Cash_Management.xlsx
+++ b/Cash_Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Business Partnering\APP DSO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92D7585-C083-4DF0-AE4F-4D6B18BA0D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9469D62C-647F-4EA2-A99D-91C20D344E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12090" yWindow="0" windowWidth="14430" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1008,7 +1008,7 @@
     <t>Limite : ce reporting mesure la trésorerie opérationnelle du cycle commercial. Pour une position bancaire complète, ajouter soldes bancaires, paie, TVA/impôts, CAPEX, dette, intérêts et lignes de crédit.</t>
   </si>
   <si>
-    <t>ds</t>
+    <t>dss</t>
   </si>
 </sst>
 </file>
@@ -11345,7 +11345,7 @@
     <row r="2" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="111" t="str">
         <f>'0_Accueil'!$D$8</f>
-        <v>ds</v>
+        <v>dss</v>
       </c>
       <c r="C2" s="83"/>
       <c r="D2" s="83"/>
@@ -12195,7 +12195,7 @@
     <row r="3" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="126" t="str">
         <f>"Société : "&amp;IF('0_Accueil'!$D$8="","Non renseignée",'0_Accueil'!$D$8)</f>
-        <v>Société : ds</v>
+        <v>Société : dss</v>
       </c>
       <c r="B3" s="126"/>
       <c r="C3" s="126"/>
